--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0056.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0056.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Phantom: Questless Knight</t>
+          <t>Hồn Ma: Kỵ Sĩ Vô Mục</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Tờ ghi chú do Carlotta để lại</t>
+          <t>Một mảnh giấy do Carlotta để lại.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Làn đường</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Ganquan</t>
+          <t>Cảm Tuyền</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Honorable Gladiator</t>
+          <t>Dũng Sĩ Đáng Kính</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Manne</t>
+          <t>Mannequin</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Budee</t>
+          <t>Bụi</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Mở Lưu Trữ Giai Điệu</t>
+          <t>Mở Kho Lưu Trữ Giai Điệu</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Viên "ngọc" của Carlotta</t>
+          <t>viên "ngọc" của Carlotta</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Xian'ge</t>
+          <t>Hiên Ca</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Debiao</t>
+          <t>Đức Biểu</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Thương nhân Roya trẻ tuổi</t>
+          <t>Thương Nhân Roya Trẻ</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Enter "Hidden Cave"</t>
+          <t>Vào "Hidden Cave"</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Nói chuyện với Ahab</t>
+          <t>Nói chuyện với Ahab đi.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Lili</t>
+          <t>Lý Ly</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Mad King: Caligula</t>
+          <t>Vua Điên: Caligula</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Reconnaissance Mô-đun</t>
+          <t>Mô-đun Trinh Sát</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Creeping Torchpine Cone</t>
+          <t>Nón Thông Đuốc Leo</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Unfreeze Statue Mirror Lối chơi</t>
+          <t>Trò Chơi Gương Tượng Giải Đông Băng</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Group Refresher</t>
+          <t>Nước Giải Khát Nhóm</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Impermanence Heron: Cyclone</t>
+          <t>Heron Vô Thường: Lốc Xoáy</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Nhân viên</t>
+          <t>Nhân Viên</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Info Tablet</t>
+          <t>Bản Ghi Thông Tin</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Aurae</t>
+          <t>Hồng Quang</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Enter Data Space</t>
+          <t>Truy cập Không Gian Dữ Liệu</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Rimewisp</t>
+          <t>Tinh Linh Băng</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Gấu lửa dường như muốn được ôm</t>
+          <t>Con gấu lò sưởi này có vẻ muốn được ôm ấy</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Shouting Vendor</t>
+          <t>Người Bán Hàng Gào Thét</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Peaceful Male</t>
+          <t>Người đàn ông hiền hòa</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Mở cánh cửa bí mật</t>
+          <t>Mở cánh cửa bí mật đi</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Universal Training Automaton</t>
+          <t>Máy Huấn Luyện Chung</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Recovering Patient</t>
+          <t>Bệnh Nhân Đang Hồi Phục</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Group AI Manager</t>
+          <t>Quản lý Bảng AI</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Arias of Past Days</t>
+          <t>: Khúc Aria Ngày Xưa</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Kronapuff</t>
+          <t>Bông Tuyết Hắc Ám</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Hooscamp Flinger</t>
+          <t>Quái Hooscamp Ném Vật</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Frostbite Coleoid</t>
+          <t>Mực Băng Giá Coleoid</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Wingray</t>
+          <t>Tia Cánh</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Di chuyển qua khe hở</t>
+          <t>Chui qua khe hở</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Angry Fluffguin</t>
+          <t>Chú Chim Cánh Cụt Bông Tức Giận</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>: "Broken Scarecrow"</t>
+          <t>: "Bù Nhìn Gãy"</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Ying</t>
+          <t>Doanh</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Chop Chop: Rightless</t>
+          <t>Chop Chop: Không Tay Phải</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Ác mộng: Feilian Beringal - Nanh Vuốt Tàn Ác</t>
+          <t>Ác Mộng: Feilian Beringal - Fangs of Cruelty</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Roccia Cube</t>
+          <t>Khối lập phương Roccia</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>"Silent Avatar"</t>
+          <t>"Hóa Thân Vô Thanh"</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Hào quang kỳ lạ</t>
+          <t>Hơi hướng kỳ bí</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Windlash Coleoid</t>
+          <t>Mực Gió Giật</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Ghi Chép</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>: Dreamscape Helix</t>
+          <t>: Xoắn Ốc Cảnh Mộng</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Injured Patroller</t>
+          <t>Lính Tuần Tra Bị Thương</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Lâu rồi không gặp</t>
+          <t>Đã lâu không gặp</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Khách Sạn</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Về bản thân bạn</t>
+          <t>Về bản thân ta</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Bell Crab</t>
+          <t>Cua Chuông</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Vào Trạm Không Gian</t>
+          <t>Bước vào Trạm Không Gian</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Đi xuống tầng dưới</t>
+          <t>Xuống tầng dưới đi</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Remove Frozen Status</t>
+          <t>Gỡ Trạng Thái Đông Cứng</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Roadblock</t>
+          <t>Chướng Ngại Đường</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Gondola Guide</t>
+          <t>Hướng dẫn viên Gondola</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Xuống dưới</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Sửa chữa</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Khu Vực Thử Thách I</t>
+          <t>Khu vực thử thách I</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Đi tưới hoa</t>
+          <t>Đi tưới hoa đi</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Camellya Cube</t>
+          <t>Khối Camellya</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Mya</t>
+          <t>Mya...</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Rời khỏi lớp học</t>
+          <t>Rời khỏi phòng học</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Qinghe</t>
+          <t>Thanh Hà</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Sniper Rifle</t>
+          <t>Súng bắn tỉa</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Calcharo_Shadow</t>
+          <t>Calcharo_Bóng Ma</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Denia's "Bedroom"</t>
+          <t>"Phòng ngủ" của Denia</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Học sinh đầy hy vọng</t>
+          <t>Học Sinh Đầy Hy Vọng</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Grandino Agent</t>
+          <t>Đặc vụ Grandino</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Little Caius</t>
+          <t>Caius Nhỏ</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Lắng nghe "tiếng vọng" của "cô ấy"</t>
+          <t>Lắng nghe tiếng vọng của "cô ấy"</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Quay về nơi bạn lần đầu hạ cánh tại Thành phố Honami</t>
+          <t>Quay lại nơi ngươi lần đầu đặt chân đến thành Honami</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Fractsidus Executioner</t>
+          <t>Đao Phủ Fractsidus</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Spline</t>
+          <t>Đường Cong</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>A Little Girl's Phantom</t>
+          <t>Bóng Ma Của Một Bé Gái</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Shitou</t>
+          <t>Thạch Đầu</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Vẻ đẹp của cô ấy vượt trên cả pháo hoa</t>
+          <t>Vẻ Đẹp Của Nàng Vượt Qua Cả Pháo Hoa</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Bridged Dreamscape</t>
+          <t>Giấc Mộng Kết Nối</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Mysterious Chest</t>
+          <t>Rương Bí Ẩn</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Withers</t>
+          <t>Héo Tàn</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Scared Fluffguin</t>
+          <t>Chim Cánh Lông Sợ Hãi</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Ta-da</t>
+          <t>Tadaa!</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Ký ức luyện tập</t>
+          <t>Ký Ức Luyện Tập</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Cô gái nhút nhát</t>
+          <t>Cô gái rụt rè</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Mutant Organism: Roseshroom Large</t>
+          <t>Sinh Vật Đột Biến: Roseshroom Large</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Whining Aix's Mire Elevator Plate</t>
+          <t>Bãi Lầy Aix Rên Rỉ - Tấm Nâng Thủy Lực</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Nhờ Cartethyia giúp đỡ</t>
+          <t>Nhờ Cartethyia trợ giúp</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Template Generator</t>
+          <t>Máy Tạo Mẫu</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Crown of Undying Flame</t>
+          <t>: Crown of Undying Flame</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Stone Rose</t>
+          <t>Hoa Đá</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Nova</t>
+          <t>Tân Tinh</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Người đàn ông ngắm đá</t>
+          <t>Người Đàn Ông Ngắm Đá</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>dnt/My monster spawner</t>
+          <t>đừng/Thiết bị triệu hồi quái vật của ta</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Lynae say mê trò chơi</t>
+          <t>Lynae đắm chìm trong trò chơi</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Viscum Berry</t>
+          <t>Quả Tầm Gửi</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Lost Roya</t>
+          <t>Roya Lạc Lối</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Recording Machine</t>
+          <t>Máy Ghi Âm</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Cô gái thân thiện</t>
+          <t>Cô Gái Thân Thiện</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Enthusiastic Male</t>
+          <t>Chàng Trai Nhiệt Huyết</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Nhãn dán trên bảng phi tiêu</t>
+          <t>Sticker trên Bảng Phi Tiêu</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Bước vào giấc mơ "bí ẩn"</t>
+          <t>Đi vào giấc mơ "bí ẩn"</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Character Environment solo placeholder</t>
+          <t>Placeholder môi trường nhân vật đơn</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Tắt</t>
+          <t>Tắt đi</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>5-Star Assessor</t>
+          <t>Đánh Giá Viên 5 Sao</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>About Verina</t>
+          <t>Về Verina</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Kỹ sư lang thang và lảm nhảm</t>
+          <t>Kỹ Sư Lang Thang Vô Định</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Photon Barrier Lock - Base</t>
+          <t>Khóa Chắn Photon - Cơ Bản</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Gatekeeper</t>
+          <t>Người Gác Cổng</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu bối rối</t>
+          <t>Nhà Nghiên Cứu Rối Bời</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Huaijin</t>
+          <t>Hoài Cận</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Nhân viên Kho - Diễn viên 1</t>
+          <t>Nhân Viên Kho Tàng - Diễn Viên 1</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Phantom: Twin Nova Nebulous Cannon</t>
+          <t>Phantom: Song Tinh Vân Đại Bác Tinh Vân</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu hay nói chuyện</t>
+          <t>Nhà Nghiên Cứu Lắm Lời</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Ancient Monument Striker</t>
+          <t>Kẻ Đánh Phá Bia Cổ</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>: Starward Handmaiden</t>
+          <t>: Nữ Tì Hướng Tinh</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Giao sách</t>
+          <t>Giao cuốn sách đi</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Blurred Figure</t>
+          <t>Hình Dáng Mờ Nhạt</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Qiaomu</t>
+          <t>Xảo Mộc</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Mysterious Package</t>
+          <t>Gói Hàng Bí Ẩn</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Đến cuối Con đường Lang thang</t>
+          <t>Đến End of Wandering</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Zhiyu</t>
+          <t>Chí Dụ</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Cô gái Royan nhiệt huyết</t>
+          <t>Cô Gái Royan sôi nổi</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>"Trader"</t>
+          <t>"Thương Nhân"</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Delicious Soliskin</t>
+          <t>Da Solis ngon quá</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Abyssal Gunmaster</t>
+          <t>Thợ Súng Vực Sâu</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Hướng dẫn Đêm Tưởng Nhớ</t>
+          <t>Hướng Dẫn Đêm Tưởng Niệm</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Cư dân Hồng Trấn</t>
+          <t>Cư Dân Hoằng Trấn</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Mở cửa</t>
+          <t>Mở cửa thôi</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Wonder Bubble</t>
+          <t>Bong Bóng Kỳ Diệu</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Augusta có thể phá hủy 3</t>
+          <t>Augusta có thể bị phá hủy 3</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Đạt Cấp 2 Trung Tâm Dữ Liệu để mở khóa</t>
+          <t>Đạt Cấp Trung Tâm Dữ Liệu 2 để mở khóa.</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Synthesize</t>
+          <t>Tổng hợp</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Insufficient Stability</t>
+          <t>Không đủ Độ Ổn Định</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Container</t>
+          <t>Thùng chứa</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Rương Cung Cấp Cao Cấp</t>
+          <t>Premium Supply Chest</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Bắt đầu chế tạo vũ khí</t>
+          <t>Bắt đầu Chế Tạo Vũ Khí</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu tập sự</t>
+          <t>Nghiên cứu viên tập sự</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Electric Current Circuit</t>
+          <t>Mạch Dòng Điện</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Gidion</t>
+          <t>Gideon</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Kuangda</t>
+          <t>Kuangda!</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Nightmare: Hecate</t>
+          <t>Ác Mộng: Hecate</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Azure Lizard</t>
+          <t>Thằn Lằn Lam</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Cựu Trưởng ban Ám Ảnh của Fisalia</t>
+          <t>Nỗi Ám Ảnh Của Cố Thủ Hiến Fisalia</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Wenshui</t>
+          <t>Văn Thủy</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Hồi tưởng lại thời khắc Bão Hư Không tấn công Lahai-Roi</t>
+          <t>Hồi tưởng lại thời khắc Bão Hư Không ập vào Lahai-Roi</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Kiểm tra bản ghi Cassette</t>
+          <t>Kiểm tra bản thu băng cassette</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Venerable Shepherd</t>
+          <t>Mục Sư Đáng Kính</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Tôi muốn một thứ gì đó</t>
+          <t>Ta muốn một cái gì đó...</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Fractsidus Cannoneer</t>
+          <t>Pháo Thủ Fractsidus</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Activate</t>
+          <t>Kích Hoạt</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Clang Bang_sàn băng có thể phá hủy</t>
+          <t>Ầm Dội_sàn băng dễ vỡ</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Galecrest Gladiator</t>
+          <t>Dũng Sĩ Gale Crest</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Fengshan</t>
+          <t>Phong Sơn</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Xiaohe</t>
+          <t>Tiểu Hạ</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Mảnh Ký Ức tìm thấy bên trong Dark Tide</t>
+          <t>Mảnh Ký Ức tìm thấy bên trong Dòng Thủy Tối</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Phrolova's Ultimate - Hecate</t>
+          <t>Kỹ năng tối thượng của Phrolova - Hecate</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Contemplative Duelist</t>
+          <t>Đấu Sĩ Trầm Ngâm</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Tiếp tục thám hiểm</t>
+          <t>Tiếp tục khám phá</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Làm theo hướng dẫn của Sumika đến khu vực tiếp theo</t>
+          <t>Đi theo sự hướng dẫn của Sumika đến khu vực tiếp theo</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Shifty-eyed Septimontian</t>
+          <t>Kẻ Láu Cá Septimontian</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Biscotti</t>
+          <t>Bánh quy Biscotti</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Mèo</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Chuyển thiết kế sàn thành "Lumen"</t>
+          <t>Đổi thiết kế sàn thành "Lumen"</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Chop Chop: Headless</t>
+          <t>Chop Chop: Không Đầu</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Nhân viên Kho B</t>
+          <t>Nhân viên Ngân hàng B</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Onlooker</t>
+          <t>Người xem</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Leftless</t>
+          <t>Không còn lối rẽ trái</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Lorelei's Kindred</t>
+          <t>Dòng Dõi Lorelei</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Tiếp tục thám hiểm</t>
+          <t>Tiếp tục khám phá</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Tethys Hub</t>
+          <t>Trung Tâm Tethys</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Sample Range</t>
+          <t>Vùng Mẫu Thử</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Vào "Thư Viện Lớn"</t>
+          <t>Bước vào "Thư Viện Vĩ Đại"</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Thành viên đội bóng tức giận</t>
+          <t>Thành Viên Nhóm Cuồng Nộ</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Xiulan</t>
+          <t>Tú Lan</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Carefully Kept Notebooks</t>
+          <t>Những Cuốn Sổ Ghi Chép Cẩn Thận</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Signboard 01</t>
+          <t>Bảng Hiệu 01</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Gate: 1</t>
+          <t>Cổng: 1</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Đến Hạ Cấp</t>
+          <t>Tới Hạng Thấp</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Wary Outcast</t>
+          <t>Kẻ ngoài cuộc cảnh giác</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Bunnywort</t>
+          <t>Cỏ thỏ tai</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Teeny</t>
+          <t>Nhóc Con</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Ký ức Vỡ Tan</t>
+          <t>Ký Ức Của Sự Tan Vỡ</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Forget-Me-Not</t>
+          <t>Hoa Lưu Ly</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Fervent Collector</t>
+          <t>Nhà Sưu Tầm Nhiệt Huyết</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Sacred Flame Altar</t>
+          <t>Bàn Thờ Lửa Thiêng</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Sound Emulator</t>
+          <t>Bộ Mô Phỏng Âm Thanh</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Lo Lắng</t>
+          <t>Nhà Nghiên Cứu Hồi Hộp</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Levitation Regression: Bridge</t>
+          <t>Hồi Quy Bay Lơ Lửng: Cầu</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>: Accursed Nightmare</t>
+          <t>: Ác Mộng Đen Tối</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Feeble Exile</t>
+          <t>Kẻ lưu đày yếu đuối</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Nhân Viên Tiếp Tân</t>
+          <t>Nhân viên Tiếp Tân</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Zhihuai</t>
+          <t>Chí Hoài</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Nói Chuyện Với DJ</t>
+          <t>Nói chuyện với DJ</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Offshoot Core</t>
+          <t>Lõi Nhánh</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>KU-Fight</t>
+          <t>KU-Chiến Đấu</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Thành Viên Hiệp Hội Tiên Phong Nữ</t>
+          <t>Thành viên Hiệp Hội Tiên Phong</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Shabby Book</t>
+          <t>Quyển Sách Cũ Kỹ</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Lấy thẻ thông hành</t>
+          <t>Lấy thẻ cấp phép đi</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Bắt Đầu Khám Phá Lại</t>
+          <t>Bắt đầu lại thám hiểm</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Khách Hàng Lo Âu</t>
+          <t>Khách Hàng Lo Lắng</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Trò Chuyện</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Freeze Frame: Những Khoảnh Khắc Nổi Bật</t>
+          <t>Định Hình: Điểm Nổi Bật Hành Động</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Bắt Đầu Thử Thách</t>
+          <t>Bắt đầu Thử thách</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>test/Cổng</t>
+          <t>test/Cánh Cổng</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Tương Tác Để Biến Hình</t>
+          <t>Tương Tác để Biến Hình</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Khách Hàng B Hoảng Sợ</t>
+          <t>Khách hàng B hoảng loạn</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Barefoot Geese</t>
+          <t>Những Chú Ngỗng Chân Trần</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Hóa Giải Trạng Thái Đông Cứng Cho Tượng Có Năng Lượng</t>
+          <t>Kích Hoạt Tượng Đá Năng Lượng Trong Trận Đấu</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Resonant Calcite</t>
+          <t>Canxit Cộng Hưởng</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Scarletthorn</t>
+          <t>Gai Đỏ Thẫm</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Chuyển Sang Bối Cảnh Starfield</t>
+          <t>Chuyển sang không gian nền Sao Trời</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Trophy Chest</t>
+          <t>Rương Thưởng Tiêu Chuẩn</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Vào Thử Thách "Rèn Luyện"</t>
+          <t>Tham gia "Thử Thách Giả Mạo"</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Heguang</t>
+          <t>Hà Quang</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Holographic Projector_Platform</t>
+          <t>Bệ Phát Hologram</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Lianfeng</t>
+          <t>Liên Phong</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Nhân viên Kho A</t>
+          <t>Nhân viên Ngân hàng A</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Giao bản nhạc 1</t>
+          <t>Giao bản nhạc số 1 đi</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Weiqi Board</t>
+          <t>Bàn cờ Vây</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>sàn băng có thể phá vỡ thông thường</t>
+          <t>sàn băng dễ vỡ</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Phantom: Vitreum Dancer</t>
+          <t>Phantom: Vũ Công Pha Lê</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Sympathetic Shepherd</t>
+          <t>Người Chăn Cừu Đồng Cảm</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Quay về bến tàu</t>
+          <t>Quay lại bến tàu</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Dreaming Deep</t>
+          <t>Giấc Mơ Sâu Thẳm</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Turtle: Bell-Borne Geochelone</t>
+          <t>Rùa: Bell-Borne Geochelone</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Đến Hồ Linh Hồn</t>
+          <t>Đến Hồ Linh Hồn thôi</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Front Desk Attendant</t>
+          <t>Nhân viên lễ tân</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Bước vào cánh cổng bí ẩn</t>
+          <t>Bước qua cánh cổng bí ẩn kia.</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Young Listener</t>
+          <t>Thính Giả Nhỏ</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Rương kho báu cho việc Dọn Dẹp</t>
+          <t>Rương Kho Báu Dành Cho Người Chiến Thắng</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>: Homebound Starfarer</t>
+          <t>: Lữ Khách Trở Về</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Đến tầng dưới</t>
+          <t>Xuống tầng dưới</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Nhà Nghiên cứu Theo Dõi</t>
+          <t>Nhà Nghiên Cứu Theo Dõi</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Dungeon 88</t>
+          <t>Hầm 88</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>điểm sáng tương tác</t>
+          <t>Điểm sáng tương tác</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Đọc Hàng Tháng Trạm</t>
+          <t>Báo Cáo Hàng Tháng Trạm</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Mở khóa Thử Thách Tacet Field ở Cấp Độ Liên Minh 19</t>
+          <t>Mở khóa Thử Thách Tổ Tacet khi đạt Cấp Hội 19</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Place Melody Capsule</t>
+          <t>Đặt Melody Capsule</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Bước vào cõi Ác Mộng</t>
+          <t>Bước vào Cõi Ác Mộng</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Waiting Wootter</t>
+          <t>Chờ Wootter</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Nightmare: Impermanence Heron - Wings of Exhaustion</t>
+          <t>Ác Mộng: Impermanence Heron - Wings of Exhaustion</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>chip Court of Savantae</t>
+          <t>Chip Tòa Savantae</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Supply Chest</t>
+          <t>Rương cung cấp tiêu chuẩn</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Gray Ridge Bull</t>
+          <t>Bò Xám Vách Núi</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Rời "Hidden Cave"</t>
+          <t>Rời "Hang Động Ẩn"</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Nhận Mảnh Vỡ</t>
+          <t>Nhận được Mảnh Vỡ</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Tay nắm cửa không nhúc nhích</t>
+          <t>Tay nắm cửa không chịu nhúc nhích.</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Lắng nghe ảo ảnh</t>
+          <t>Hãy lắng nghe những ảo ảnh</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Bước vào Lost Beyond</t>
+          <t>Bước vào Thế Giới Bị Lãng Quên</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Lady Guan</t>
+          <t>Quý cô Guan</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Rời Sonoro Sphere</t>
+          <t>Rời khỏi Sonoro Sphere đi</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Fractsidus Cannoneer</t>
+          <t>Pháo Thủ Fractsidus</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Shy Commoner</t>
+          <t>Dân thường e thẹn</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Phoebe Cube</t>
+          <t>Khối Phoebe</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>: Rotting Yellow</t>
+          <t>: Vàng Mục Nát</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Kiếm Acorus</t>
+          <t>Sword Acorus</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Tricolor</t>
+          <t>Ba Màu</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Tàn Tích Có Thể Phá Hủy: Bãi Lầy Whining Aix</t>
+          <t>Bãi Lầy Aix Rên Rỉ - Tàn Tích Có Thể Phá Hủy A</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Quý Bà Biển Cả</t>
+          <t>Nữ Thần Biển Cả</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
